--- a/Vontobel_Files/Vontobel_trades.xlsx
+++ b/Vontobel_Files/Vontobel_trades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/Vontobel_Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_0B4E91BF92AC470D6D4185E586244CE3E506B7AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89D47B1C-396C-4D3E-917B-EE29D210A65E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_0B4E91BF92AC47DDE331157C12A475DDE406B515" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59EDA1B0-2D63-4BD8-99CE-532B4BE7645C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Account Name</t>
   </si>
@@ -37,9 +37,15 @@
     <t>Security</t>
   </si>
   <si>
+    <t>ISIN</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>Broker</t>
   </si>
   <si>
@@ -58,9 +64,15 @@
     <t>Comgest Growth Europe EUR</t>
   </si>
   <si>
+    <t>IE00B5WN3467</t>
+  </si>
+  <si>
     <t>1076.117</t>
   </si>
   <si>
+    <t>EUR</t>
+  </si>
+  <si>
     <t>Vontobel</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
     <t>iShares STOXX Europe 600 UCITS ETF (DE) 12.02.2026 Acquisto EUR</t>
   </si>
   <si>
+    <t>DE0002635307</t>
+  </si>
+  <si>
     <t>700</t>
   </si>
   <si>
@@ -82,7 +97,13 @@
     <t>Novartis AG Namen 26.02.2026 Vendita CHF</t>
   </si>
   <si>
+    <t>CH0012005267</t>
+  </si>
+  <si>
     <t>150</t>
+  </si>
+  <si>
+    <t>CHF</t>
   </si>
 </sst>
 </file>
@@ -445,10 +466,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="61" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,80 +498,104 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 INTERNAL</oddFooter>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 CONFIDENTIAL</oddFooter>
   </headerFooter>
 </worksheet>
 </file>